--- a/Team-Data/2014-15/1-13-2014-15.xlsx
+++ b/Team-Data/2014-15/1-13-2014-15.xlsx
@@ -50,7 +50,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -66,6 +65,74 @@
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -661,64 +728,64 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E2" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F2" t="n">
         <v>8</v>
       </c>
       <c r="G2" t="n">
-        <v>0.789</v>
+        <v>0.784</v>
       </c>
       <c r="H2" t="n">
         <v>48.3</v>
       </c>
       <c r="I2" t="n">
-        <v>37.8</v>
+        <v>37.7</v>
       </c>
       <c r="J2" t="n">
-        <v>80.90000000000001</v>
+        <v>80.8</v>
       </c>
       <c r="K2" t="n">
         <v>0.467</v>
       </c>
       <c r="L2" t="n">
-        <v>9.6</v>
+        <v>9.5</v>
       </c>
       <c r="M2" t="n">
-        <v>24.8</v>
+        <v>24.9</v>
       </c>
       <c r="N2" t="n">
-        <v>0.386</v>
+        <v>0.383</v>
       </c>
       <c r="O2" t="n">
-        <v>17.8</v>
+        <v>18</v>
       </c>
       <c r="P2" t="n">
-        <v>23.2</v>
+        <v>23.4</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.768</v>
+        <v>0.772</v>
       </c>
       <c r="R2" t="n">
-        <v>8.699999999999999</v>
+        <v>8.5</v>
       </c>
       <c r="S2" t="n">
-        <v>32.7</v>
+        <v>32.8</v>
       </c>
       <c r="T2" t="n">
-        <v>41.4</v>
+        <v>41.3</v>
       </c>
       <c r="U2" t="n">
-        <v>25.7</v>
+        <v>25.4</v>
       </c>
       <c r="V2" t="n">
-        <v>14.5</v>
+        <v>14.4</v>
       </c>
       <c r="W2" t="n">
-        <v>8.9</v>
+        <v>9</v>
       </c>
       <c r="X2" t="n">
         <v>4.6</v>
@@ -733,28 +800,28 @@
         <v>21.2</v>
       </c>
       <c r="AB2" t="n">
-        <v>103</v>
+        <v>102.9</v>
       </c>
       <c r="AC2" t="n">
-        <v>6.1</v>
+        <v>5.8</v>
       </c>
       <c r="AD2" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="AE2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AF2" t="n">
         <v>2</v>
       </c>
       <c r="AG2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AH2" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AI2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AJ2" t="n">
         <v>27</v>
@@ -763,28 +830,28 @@
         <v>5</v>
       </c>
       <c r="AL2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AM2" t="n">
         <v>8</v>
       </c>
       <c r="AN2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AO2" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AP2" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AQ2" t="n">
+        <v>10</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>29</v>
+      </c>
+      <c r="AS2" t="n">
         <v>11</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>27</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>12</v>
       </c>
       <c r="AT2" t="n">
         <v>23</v>
@@ -799,22 +866,22 @@
         <v>6</v>
       </c>
       <c r="AX2" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AY2" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AZ2" t="n">
         <v>2</v>
       </c>
       <c r="BA2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="BB2" t="n">
         <v>7</v>
       </c>
       <c r="BC2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="BD2" t="n">
         <v>10</v>
@@ -826,7 +893,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>1-13-2014-15</t>
+          <t>2015-01-13</t>
         </is>
       </c>
     </row>
@@ -921,7 +988,7 @@
         <v>-1.2</v>
       </c>
       <c r="AD3" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AE3" t="n">
         <v>25</v>
@@ -933,7 +1000,7 @@
         <v>24</v>
       </c>
       <c r="AH3" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AI3" t="n">
         <v>3</v>
@@ -966,16 +1033,16 @@
         <v>17</v>
       </c>
       <c r="AS3" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AT3" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AU3" t="n">
         <v>3</v>
       </c>
       <c r="AV3" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AW3" t="n">
         <v>9</v>
@@ -987,7 +1054,7 @@
         <v>22</v>
       </c>
       <c r="AZ3" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BA3" t="n">
         <v>29</v>
@@ -1008,7 +1075,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>1-13-2014-15</t>
+          <t>2015-01-13</t>
         </is>
       </c>
     </row>
@@ -1103,16 +1170,16 @@
         <v>-2.5</v>
       </c>
       <c r="AD4" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AE4" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AF4" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AG4" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AH4" t="n">
         <v>7</v>
@@ -1142,7 +1209,7 @@
         <v>21</v>
       </c>
       <c r="AQ4" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AR4" t="n">
         <v>26</v>
@@ -1151,13 +1218,13 @@
         <v>13</v>
       </c>
       <c r="AT4" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AU4" t="n">
         <v>20</v>
       </c>
       <c r="AV4" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AW4" t="n">
         <v>21</v>
@@ -1169,7 +1236,7 @@
         <v>12</v>
       </c>
       <c r="AZ4" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BA4" t="n">
         <v>21</v>
@@ -1190,7 +1257,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>1-13-2014-15</t>
+          <t>2015-01-13</t>
         </is>
       </c>
     </row>
@@ -1285,7 +1352,7 @@
         <v>-2.9</v>
       </c>
       <c r="AD5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AE5" t="n">
         <v>21</v>
@@ -1297,7 +1364,7 @@
         <v>21</v>
       </c>
       <c r="AH5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AI5" t="n">
         <v>23</v>
@@ -1312,13 +1379,13 @@
         <v>27</v>
       </c>
       <c r="AM5" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AN5" t="n">
         <v>29</v>
       </c>
       <c r="AO5" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AP5" t="n">
         <v>16</v>
@@ -1336,7 +1403,7 @@
         <v>13</v>
       </c>
       <c r="AU5" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AV5" t="n">
         <v>1</v>
@@ -1348,7 +1415,7 @@
         <v>12</v>
       </c>
       <c r="AY5" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AZ5" t="n">
         <v>3</v>
@@ -1357,7 +1424,7 @@
         <v>7</v>
       </c>
       <c r="BB5" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BC5" t="n">
         <v>23</v>
@@ -1372,7 +1439,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>1-13-2014-15</t>
+          <t>2015-01-13</t>
         </is>
       </c>
     </row>
@@ -1467,7 +1534,7 @@
         <v>2.9</v>
       </c>
       <c r="AD6" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AE6" t="n">
         <v>5</v>
@@ -1485,7 +1552,7 @@
         <v>21</v>
       </c>
       <c r="AJ6" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AK6" t="n">
         <v>20</v>
@@ -1497,7 +1564,7 @@
         <v>17</v>
       </c>
       <c r="AN6" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AO6" t="n">
         <v>2</v>
@@ -1506,13 +1573,13 @@
         <v>2</v>
       </c>
       <c r="AQ6" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AR6" t="n">
         <v>5</v>
       </c>
       <c r="AS6" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AT6" t="n">
         <v>3</v>
@@ -1521,7 +1588,7 @@
         <v>13</v>
       </c>
       <c r="AV6" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AW6" t="n">
         <v>28</v>
@@ -1554,7 +1621,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>1-13-2014-15</t>
+          <t>2015-01-13</t>
         </is>
       </c>
     </row>
@@ -1571,16 +1638,16 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E7" t="n">
         <v>19</v>
       </c>
       <c r="F7" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G7" t="n">
-        <v>0.487</v>
+        <v>0.5</v>
       </c>
       <c r="H7" t="n">
         <v>48.1</v>
@@ -1595,49 +1662,49 @@
         <v>0.448</v>
       </c>
       <c r="L7" t="n">
-        <v>8.300000000000001</v>
+        <v>8.1</v>
       </c>
       <c r="M7" t="n">
-        <v>23.9</v>
+        <v>23.7</v>
       </c>
       <c r="N7" t="n">
-        <v>0.345</v>
+        <v>0.344</v>
       </c>
       <c r="O7" t="n">
-        <v>18.4</v>
+        <v>18.5</v>
       </c>
       <c r="P7" t="n">
-        <v>24.2</v>
+        <v>24.3</v>
       </c>
       <c r="Q7" t="n">
         <v>0.76</v>
       </c>
       <c r="R7" t="n">
-        <v>10.9</v>
+        <v>10.8</v>
       </c>
       <c r="S7" t="n">
-        <v>30.2</v>
+        <v>30.3</v>
       </c>
       <c r="T7" t="n">
         <v>41.2</v>
       </c>
       <c r="U7" t="n">
-        <v>21.8</v>
+        <v>22</v>
       </c>
       <c r="V7" t="n">
-        <v>13.9</v>
+        <v>13.8</v>
       </c>
       <c r="W7" t="n">
         <v>7.1</v>
       </c>
       <c r="X7" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="Y7" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="Z7" t="n">
-        <v>18</v>
+        <v>17.9</v>
       </c>
       <c r="AA7" t="n">
         <v>21.2</v>
@@ -1646,22 +1713,22 @@
         <v>99.8</v>
       </c>
       <c r="AC7" t="n">
-        <v>-0.3</v>
+        <v>-0.1</v>
       </c>
       <c r="AD7" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AE7" t="n">
         <v>14</v>
       </c>
       <c r="AF7" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="AG7" t="n">
         <v>14</v>
       </c>
       <c r="AH7" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AI7" t="n">
         <v>22</v>
@@ -1673,19 +1740,19 @@
         <v>18</v>
       </c>
       <c r="AL7" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AM7" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AN7" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AO7" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AP7" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AQ7" t="n">
         <v>12</v>
@@ -1694,7 +1761,7 @@
         <v>15</v>
       </c>
       <c r="AS7" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AT7" t="n">
         <v>24</v>
@@ -1712,13 +1779,13 @@
         <v>26</v>
       </c>
       <c r="AY7" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AZ7" t="n">
         <v>1</v>
       </c>
       <c r="BA7" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BB7" t="n">
         <v>17</v>
@@ -1736,7 +1803,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>1-13-2014-15</t>
+          <t>2015-01-13</t>
         </is>
       </c>
     </row>
@@ -1756,25 +1823,25 @@
         <v>38</v>
       </c>
       <c r="E8" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F8" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G8" t="n">
-        <v>0.711</v>
+        <v>0.6840000000000001</v>
       </c>
       <c r="H8" t="n">
-        <v>48.7</v>
+        <v>48.5</v>
       </c>
       <c r="I8" t="n">
-        <v>41.1</v>
+        <v>41</v>
       </c>
       <c r="J8" t="n">
-        <v>86.8</v>
+        <v>86.3</v>
       </c>
       <c r="K8" t="n">
-        <v>0.474</v>
+        <v>0.475</v>
       </c>
       <c r="L8" t="n">
         <v>9.6</v>
@@ -1783,34 +1850,34 @@
         <v>26.7</v>
       </c>
       <c r="N8" t="n">
-        <v>0.358</v>
+        <v>0.361</v>
       </c>
       <c r="O8" t="n">
         <v>17.2</v>
       </c>
       <c r="P8" t="n">
-        <v>22.7</v>
+        <v>22.6</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.759</v>
+        <v>0.762</v>
       </c>
       <c r="R8" t="n">
-        <v>10.9</v>
+        <v>10.8</v>
       </c>
       <c r="S8" t="n">
-        <v>31.6</v>
+        <v>31.4</v>
       </c>
       <c r="T8" t="n">
-        <v>42.5</v>
+        <v>42.2</v>
       </c>
       <c r="U8" t="n">
-        <v>23.8</v>
+        <v>23.7</v>
       </c>
       <c r="V8" t="n">
         <v>12.2</v>
       </c>
       <c r="W8" t="n">
-        <v>8.1</v>
+        <v>8</v>
       </c>
       <c r="X8" t="n">
         <v>5</v>
@@ -1819,37 +1886,37 @@
         <v>3.5</v>
       </c>
       <c r="Z8" t="n">
-        <v>20.2</v>
+        <v>20.1</v>
       </c>
       <c r="AA8" t="n">
-        <v>22.3</v>
+        <v>22.2</v>
       </c>
       <c r="AB8" t="n">
-        <v>109.1</v>
+        <v>108.8</v>
       </c>
       <c r="AC8" t="n">
-        <v>6.5</v>
+        <v>6.3</v>
       </c>
       <c r="AD8" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AE8" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AF8" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AG8" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AH8" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="AI8" t="n">
         <v>2</v>
       </c>
       <c r="AJ8" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AK8" t="n">
         <v>2</v>
@@ -1861,25 +1928,25 @@
         <v>5</v>
       </c>
       <c r="AN8" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AO8" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AP8" t="n">
         <v>19</v>
       </c>
       <c r="AQ8" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AR8" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AS8" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AT8" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="AU8" t="n">
         <v>7</v>
@@ -1891,13 +1958,13 @@
         <v>11</v>
       </c>
       <c r="AX8" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AY8" t="n">
         <v>2</v>
       </c>
       <c r="AZ8" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="BA8" t="n">
         <v>3</v>
@@ -1906,7 +1973,7 @@
         <v>2</v>
       </c>
       <c r="BC8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BD8" t="n">
         <v>10</v>
@@ -1918,7 +1985,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>1-13-2014-15</t>
+          <t>2015-01-13</t>
         </is>
       </c>
     </row>
@@ -2013,13 +2080,13 @@
         <v>-1.4</v>
       </c>
       <c r="AD9" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="AE9" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AF9" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AG9" t="n">
         <v>17</v>
@@ -2028,10 +2095,10 @@
         <v>14</v>
       </c>
       <c r="AI9" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AJ9" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AK9" t="n">
         <v>23</v>
@@ -2049,10 +2116,10 @@
         <v>4</v>
       </c>
       <c r="AP9" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AQ9" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AR9" t="n">
         <v>2</v>
@@ -2067,7 +2134,7 @@
         <v>17</v>
       </c>
       <c r="AV9" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AW9" t="n">
         <v>24</v>
@@ -2088,7 +2155,7 @@
         <v>9</v>
       </c>
       <c r="BC9" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="BD9" t="n">
         <v>10</v>
@@ -2100,7 +2167,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>1-13-2014-15</t>
+          <t>2015-01-13</t>
         </is>
       </c>
     </row>
@@ -2195,7 +2262,7 @@
         <v>-2.1</v>
       </c>
       <c r="AD10" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AE10" t="n">
         <v>23</v>
@@ -2207,13 +2274,13 @@
         <v>23</v>
       </c>
       <c r="AH10" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AI10" t="n">
         <v>20</v>
       </c>
       <c r="AJ10" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AK10" t="n">
         <v>29</v>
@@ -2222,16 +2289,16 @@
         <v>9</v>
       </c>
       <c r="AM10" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AN10" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AO10" t="n">
         <v>25</v>
       </c>
       <c r="AP10" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AQ10" t="n">
         <v>29</v>
@@ -2258,7 +2325,7 @@
         <v>21</v>
       </c>
       <c r="AY10" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AZ10" t="n">
         <v>10</v>
@@ -2282,7 +2349,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>1-13-2014-15</t>
+          <t>2015-01-13</t>
         </is>
       </c>
     </row>
@@ -2299,79 +2366,79 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E11" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F11" t="n">
         <v>5</v>
       </c>
       <c r="G11" t="n">
-        <v>0.857</v>
+        <v>0.853</v>
       </c>
       <c r="H11" t="n">
         <v>48.1</v>
       </c>
       <c r="I11" t="n">
-        <v>41.4</v>
+        <v>41.2</v>
       </c>
       <c r="J11" t="n">
-        <v>85.40000000000001</v>
+        <v>85.2</v>
       </c>
       <c r="K11" t="n">
         <v>0.484</v>
       </c>
       <c r="L11" t="n">
-        <v>10.1</v>
+        <v>10</v>
       </c>
       <c r="M11" t="n">
         <v>26.3</v>
       </c>
       <c r="N11" t="n">
-        <v>0.383</v>
+        <v>0.379</v>
       </c>
       <c r="O11" t="n">
-        <v>16.6</v>
+        <v>16.8</v>
       </c>
       <c r="P11" t="n">
-        <v>21.3</v>
+        <v>21.6</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.779</v>
+        <v>0.778</v>
       </c>
       <c r="R11" t="n">
-        <v>9.9</v>
+        <v>10</v>
       </c>
       <c r="S11" t="n">
-        <v>34.8</v>
+        <v>35.1</v>
       </c>
       <c r="T11" t="n">
-        <v>44.7</v>
+        <v>45.1</v>
       </c>
       <c r="U11" t="n">
-        <v>26.9</v>
+        <v>26.8</v>
       </c>
       <c r="V11" t="n">
-        <v>15.2</v>
+        <v>15.4</v>
       </c>
       <c r="W11" t="n">
-        <v>9.300000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="X11" t="n">
         <v>6.4</v>
       </c>
       <c r="Y11" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="Z11" t="n">
-        <v>20</v>
+        <v>20.1</v>
       </c>
       <c r="AA11" t="n">
         <v>18.8</v>
       </c>
       <c r="AB11" t="n">
-        <v>109.4</v>
+        <v>109.2</v>
       </c>
       <c r="AC11" t="n">
         <v>11</v>
@@ -2380,7 +2447,7 @@
         <v>30</v>
       </c>
       <c r="AE11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AF11" t="n">
         <v>1</v>
@@ -2395,7 +2462,7 @@
         <v>1</v>
       </c>
       <c r="AJ11" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AK11" t="n">
         <v>1</v>
@@ -2416,25 +2483,25 @@
         <v>24</v>
       </c>
       <c r="AQ11" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AR11" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AS11" t="n">
         <v>2</v>
       </c>
       <c r="AT11" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AU11" t="n">
         <v>1</v>
       </c>
       <c r="AV11" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AW11" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AX11" t="n">
         <v>2</v>
@@ -2443,7 +2510,7 @@
         <v>4</v>
       </c>
       <c r="AZ11" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="BA11" t="n">
         <v>27</v>
@@ -2464,7 +2531,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>1-13-2014-15</t>
+          <t>2015-01-13</t>
         </is>
       </c>
     </row>
@@ -2481,25 +2548,25 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E12" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F12" t="n">
         <v>11</v>
       </c>
       <c r="G12" t="n">
-        <v>0.703</v>
+        <v>0.711</v>
       </c>
       <c r="H12" t="n">
         <v>48.5</v>
       </c>
       <c r="I12" t="n">
-        <v>36.4</v>
+        <v>36.2</v>
       </c>
       <c r="J12" t="n">
-        <v>83.40000000000001</v>
+        <v>83.09999999999999</v>
       </c>
       <c r="K12" t="n">
         <v>0.436</v>
@@ -2508,19 +2575,19 @@
         <v>11.9</v>
       </c>
       <c r="M12" t="n">
-        <v>34.1</v>
+        <v>34</v>
       </c>
       <c r="N12" t="n">
-        <v>0.349</v>
+        <v>0.35</v>
       </c>
       <c r="O12" t="n">
-        <v>17.1</v>
+        <v>17.5</v>
       </c>
       <c r="P12" t="n">
-        <v>24.1</v>
+        <v>24.8</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.708</v>
+        <v>0.707</v>
       </c>
       <c r="R12" t="n">
         <v>12.4</v>
@@ -2529,13 +2596,13 @@
         <v>31.4</v>
       </c>
       <c r="T12" t="n">
-        <v>43.7</v>
+        <v>43.8</v>
       </c>
       <c r="U12" t="n">
         <v>20.7</v>
       </c>
       <c r="V12" t="n">
-        <v>17.4</v>
+        <v>17.3</v>
       </c>
       <c r="W12" t="n">
         <v>9.699999999999999</v>
@@ -2544,31 +2611,31 @@
         <v>4.6</v>
       </c>
       <c r="Y12" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="Z12" t="n">
-        <v>22.7</v>
+        <v>22.9</v>
       </c>
       <c r="AA12" t="n">
-        <v>20.5</v>
+        <v>20.8</v>
       </c>
       <c r="AB12" t="n">
-        <v>101.6</v>
+        <v>101.8</v>
       </c>
       <c r="AC12" t="n">
-        <v>4.6</v>
+        <v>4.9</v>
       </c>
       <c r="AD12" t="n">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="AE12" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AF12" t="n">
         <v>4</v>
       </c>
       <c r="AG12" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AH12" t="n">
         <v>11</v>
@@ -2589,13 +2656,13 @@
         <v>1</v>
       </c>
       <c r="AN12" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AO12" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="AP12" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="AQ12" t="n">
         <v>28</v>
@@ -2604,7 +2671,7 @@
         <v>4</v>
       </c>
       <c r="AS12" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AT12" t="n">
         <v>9</v>
@@ -2619,19 +2686,19 @@
         <v>2</v>
       </c>
       <c r="AX12" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AY12" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="AZ12" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="BA12" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="BB12" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BC12" t="n">
         <v>7</v>
@@ -2646,7 +2713,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>1-13-2014-15</t>
+          <t>2015-01-13</t>
         </is>
       </c>
     </row>
@@ -2663,64 +2730,64 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E13" t="n">
         <v>15</v>
       </c>
       <c r="F13" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G13" t="n">
-        <v>0.375</v>
+        <v>0.385</v>
       </c>
       <c r="H13" t="n">
         <v>48.4</v>
       </c>
       <c r="I13" t="n">
-        <v>36</v>
+        <v>35.9</v>
       </c>
       <c r="J13" t="n">
-        <v>84</v>
+        <v>84.09999999999999</v>
       </c>
       <c r="K13" t="n">
-        <v>0.428</v>
+        <v>0.427</v>
       </c>
       <c r="L13" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="M13" t="n">
-        <v>20.8</v>
+        <v>20.9</v>
       </c>
       <c r="N13" t="n">
-        <v>0.338</v>
+        <v>0.339</v>
       </c>
       <c r="O13" t="n">
-        <v>16.5</v>
+        <v>16.4</v>
       </c>
       <c r="P13" t="n">
-        <v>22</v>
+        <v>21.8</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.749</v>
+        <v>0.754</v>
       </c>
       <c r="R13" t="n">
         <v>11.2</v>
       </c>
       <c r="S13" t="n">
-        <v>34.1</v>
+        <v>34.2</v>
       </c>
       <c r="T13" t="n">
-        <v>45.3</v>
+        <v>45.4</v>
       </c>
       <c r="U13" t="n">
-        <v>20.8</v>
+        <v>20.7</v>
       </c>
       <c r="V13" t="n">
-        <v>14.4</v>
+        <v>14.3</v>
       </c>
       <c r="W13" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="X13" t="n">
         <v>4.7</v>
@@ -2729,28 +2796,28 @@
         <v>5.2</v>
       </c>
       <c r="Z13" t="n">
+        <v>21.1</v>
+      </c>
+      <c r="AA13" t="n">
         <v>21</v>
       </c>
-      <c r="AA13" t="n">
-        <v>21.1</v>
-      </c>
       <c r="AB13" t="n">
-        <v>95.5</v>
+        <v>95.3</v>
       </c>
       <c r="AC13" t="n">
-        <v>-1.6</v>
+        <v>-1.4</v>
       </c>
       <c r="AD13" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AE13" t="n">
         <v>21</v>
       </c>
       <c r="AF13" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AG13" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AH13" t="n">
         <v>19</v>
@@ -2759,16 +2826,16 @@
         <v>27</v>
       </c>
       <c r="AJ13" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AK13" t="n">
         <v>28</v>
       </c>
       <c r="AL13" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AM13" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AN13" t="n">
         <v>22</v>
@@ -2777,10 +2844,10 @@
         <v>23</v>
       </c>
       <c r="AP13" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AQ13" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="AR13" t="n">
         <v>12</v>
@@ -2804,19 +2871,19 @@
         <v>15</v>
       </c>
       <c r="AY13" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AZ13" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="BA13" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BB13" t="n">
         <v>26</v>
       </c>
       <c r="BC13" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="BD13" t="n">
         <v>10</v>
@@ -2828,7 +2895,7 @@
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>1-13-2014-15</t>
+          <t>2015-01-13</t>
         </is>
       </c>
     </row>
@@ -2923,10 +2990,10 @@
         <v>6.4</v>
       </c>
       <c r="AD14" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AE14" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AF14" t="n">
         <v>9</v>
@@ -2944,7 +3011,7 @@
         <v>21</v>
       </c>
       <c r="AK14" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AL14" t="n">
         <v>2</v>
@@ -2953,7 +3020,7 @@
         <v>4</v>
       </c>
       <c r="AN14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AO14" t="n">
         <v>6</v>
@@ -2962,7 +3029,7 @@
         <v>6</v>
       </c>
       <c r="AQ14" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AR14" t="n">
         <v>28</v>
@@ -2971,13 +3038,13 @@
         <v>15</v>
       </c>
       <c r="AT14" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AU14" t="n">
         <v>5</v>
       </c>
       <c r="AV14" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AW14" t="n">
         <v>13</v>
@@ -2998,7 +3065,7 @@
         <v>5</v>
       </c>
       <c r="BC14" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BD14" t="n">
         <v>10</v>
@@ -3010,7 +3077,7 @@
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>1-13-2014-15</t>
+          <t>2015-01-13</t>
         </is>
       </c>
     </row>
@@ -3042,118 +3109,118 @@
         <v>48.4</v>
       </c>
       <c r="I15" t="n">
-        <v>37.9</v>
+        <v>37.8</v>
       </c>
       <c r="J15" t="n">
-        <v>86.7</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="K15" t="n">
-        <v>0.437</v>
+        <v>0.438</v>
       </c>
       <c r="L15" t="n">
         <v>7.1</v>
       </c>
       <c r="M15" t="n">
-        <v>20.2</v>
+        <v>19.8</v>
       </c>
       <c r="N15" t="n">
-        <v>0.351</v>
+        <v>0.356</v>
       </c>
       <c r="O15" t="n">
-        <v>18.2</v>
+        <v>18.7</v>
       </c>
       <c r="P15" t="n">
-        <v>24.4</v>
+        <v>25</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.745</v>
+        <v>0.747</v>
       </c>
       <c r="R15" t="n">
-        <v>11.7</v>
+        <v>11.6</v>
       </c>
       <c r="S15" t="n">
-        <v>31.7</v>
+        <v>31.5</v>
       </c>
       <c r="T15" t="n">
-        <v>43.4</v>
+        <v>43.1</v>
       </c>
       <c r="U15" t="n">
-        <v>20.9</v>
+        <v>20.8</v>
       </c>
       <c r="V15" t="n">
         <v>12.5</v>
       </c>
       <c r="W15" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="X15" t="n">
         <v>4.7</v>
       </c>
       <c r="Y15" t="n">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="Z15" t="n">
-        <v>21.3</v>
+        <v>21.8</v>
       </c>
       <c r="AA15" t="n">
-        <v>20.3</v>
+        <v>20.7</v>
       </c>
       <c r="AB15" t="n">
-        <v>101</v>
+        <v>101.4</v>
       </c>
       <c r="AC15" t="n">
-        <v>-5.7</v>
+        <v>-6.1</v>
       </c>
       <c r="AD15" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AE15" t="n">
         <v>27</v>
       </c>
       <c r="AF15" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AG15" t="n">
         <v>27</v>
       </c>
       <c r="AH15" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AI15" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AJ15" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AK15" t="n">
         <v>24</v>
       </c>
       <c r="AL15" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AM15" t="n">
         <v>22</v>
       </c>
       <c r="AN15" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AO15" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AP15" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AQ15" t="n">
         <v>20</v>
       </c>
       <c r="AR15" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AS15" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AT15" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AU15" t="n">
         <v>19</v>
@@ -3162,22 +3229,22 @@
         <v>4</v>
       </c>
       <c r="AW15" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AX15" t="n">
         <v>16</v>
       </c>
       <c r="AY15" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AZ15" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="BA15" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="BB15" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BC15" t="n">
         <v>27</v>
@@ -3192,7 +3259,7 @@
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>1-13-2014-15</t>
+          <t>2015-01-13</t>
         </is>
       </c>
     </row>
@@ -3287,7 +3354,7 @@
         <v>3.7</v>
       </c>
       <c r="AD16" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="AE16" t="n">
         <v>5</v>
@@ -3308,7 +3375,7 @@
         <v>15</v>
       </c>
       <c r="AK16" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AL16" t="n">
         <v>28</v>
@@ -3320,22 +3387,22 @@
         <v>12</v>
       </c>
       <c r="AO16" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AP16" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AQ16" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AR16" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AS16" t="n">
         <v>16</v>
       </c>
       <c r="AT16" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AU16" t="n">
         <v>10</v>
@@ -3350,19 +3417,19 @@
         <v>22</v>
       </c>
       <c r="AY16" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AZ16" t="n">
         <v>9</v>
       </c>
       <c r="BA16" t="n">
+        <v>16</v>
+      </c>
+      <c r="BB16" t="n">
         <v>14</v>
       </c>
-      <c r="BB16" t="n">
-        <v>13</v>
-      </c>
       <c r="BC16" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="BD16" t="n">
         <v>10</v>
@@ -3374,7 +3441,7 @@
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>1-13-2014-15</t>
+          <t>2015-01-13</t>
         </is>
       </c>
     </row>
@@ -3391,16 +3458,16 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E17" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F17" t="n">
         <v>21</v>
       </c>
       <c r="G17" t="n">
-        <v>0.447</v>
+        <v>0.432</v>
       </c>
       <c r="H17" t="n">
         <v>48</v>
@@ -3409,70 +3476,70 @@
         <v>34.3</v>
       </c>
       <c r="J17" t="n">
-        <v>74.40000000000001</v>
+        <v>74.3</v>
       </c>
       <c r="K17" t="n">
-        <v>0.461</v>
+        <v>0.462</v>
       </c>
       <c r="L17" t="n">
-        <v>7.2</v>
+        <v>7.3</v>
       </c>
       <c r="M17" t="n">
-        <v>20.8</v>
+        <v>20.9</v>
       </c>
       <c r="N17" t="n">
-        <v>0.346</v>
+        <v>0.351</v>
       </c>
       <c r="O17" t="n">
-        <v>17.9</v>
+        <v>18.1</v>
       </c>
       <c r="P17" t="n">
-        <v>24.4</v>
+        <v>24.7</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.732</v>
+        <v>0.733</v>
       </c>
       <c r="R17" t="n">
         <v>8.4</v>
       </c>
       <c r="S17" t="n">
-        <v>28.4</v>
+        <v>28.1</v>
       </c>
       <c r="T17" t="n">
-        <v>36.9</v>
+        <v>36.5</v>
       </c>
       <c r="U17" t="n">
-        <v>20</v>
+        <v>19.9</v>
       </c>
       <c r="V17" t="n">
-        <v>14.5</v>
+        <v>14.4</v>
       </c>
       <c r="W17" t="n">
         <v>8.4</v>
       </c>
       <c r="X17" t="n">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="Y17" t="n">
         <v>4.3</v>
       </c>
       <c r="Z17" t="n">
-        <v>20.1</v>
+        <v>20.2</v>
       </c>
       <c r="AA17" t="n">
-        <v>20.7</v>
+        <v>20.8</v>
       </c>
       <c r="AB17" t="n">
-        <v>93.59999999999999</v>
+        <v>94</v>
       </c>
       <c r="AC17" t="n">
-        <v>-3.8</v>
+        <v>-4</v>
       </c>
       <c r="AD17" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="AE17" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AF17" t="n">
         <v>18</v>
@@ -3493,19 +3560,19 @@
         <v>11</v>
       </c>
       <c r="AL17" t="n">
+        <v>15</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>18</v>
+      </c>
+      <c r="AN17" t="n">
         <v>16</v>
       </c>
-      <c r="AM17" t="n">
-        <v>19</v>
-      </c>
-      <c r="AN17" t="n">
-        <v>18</v>
-      </c>
       <c r="AO17" t="n">
+        <v>9</v>
+      </c>
+      <c r="AP17" t="n">
         <v>10</v>
-      </c>
-      <c r="AP17" t="n">
-        <v>8</v>
       </c>
       <c r="AQ17" t="n">
         <v>26</v>
@@ -3520,7 +3587,7 @@
         <v>30</v>
       </c>
       <c r="AU17" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AV17" t="n">
         <v>12</v>
@@ -3532,13 +3599,13 @@
         <v>28</v>
       </c>
       <c r="AY17" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AZ17" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BA17" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BB17" t="n">
         <v>28</v>
@@ -3556,7 +3623,7 @@
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>1-13-2014-15</t>
+          <t>2015-01-13</t>
         </is>
       </c>
     </row>
@@ -3651,7 +3718,7 @@
         <v>0.8</v>
       </c>
       <c r="AD18" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AE18" t="n">
         <v>13</v>
@@ -3663,16 +3730,16 @@
         <v>13</v>
       </c>
       <c r="AH18" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AI18" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AJ18" t="n">
         <v>23</v>
       </c>
       <c r="AK18" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AL18" t="n">
         <v>22</v>
@@ -3681,7 +3748,7 @@
         <v>24</v>
       </c>
       <c r="AN18" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AO18" t="n">
         <v>24</v>
@@ -3708,7 +3775,7 @@
         <v>28</v>
       </c>
       <c r="AW18" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AX18" t="n">
         <v>19</v>
@@ -3717,13 +3784,13 @@
         <v>13</v>
       </c>
       <c r="AZ18" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="BA18" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BB18" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BC18" t="n">
         <v>13</v>
@@ -3738,7 +3805,7 @@
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>1-13-2014-15</t>
+          <t>2015-01-13</t>
         </is>
       </c>
     </row>
@@ -3755,61 +3822,61 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E19" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F19" t="n">
         <v>31</v>
       </c>
       <c r="G19" t="n">
-        <v>0.162</v>
+        <v>0.139</v>
       </c>
       <c r="H19" t="n">
         <v>48.3</v>
       </c>
       <c r="I19" t="n">
-        <v>37.3</v>
+        <v>37.2</v>
       </c>
       <c r="J19" t="n">
         <v>85.5</v>
       </c>
       <c r="K19" t="n">
-        <v>0.436</v>
+        <v>0.435</v>
       </c>
       <c r="L19" t="n">
-        <v>5.1</v>
+        <v>4.9</v>
       </c>
       <c r="M19" t="n">
-        <v>14.9</v>
+        <v>14.8</v>
       </c>
       <c r="N19" t="n">
-        <v>0.341</v>
+        <v>0.335</v>
       </c>
       <c r="O19" t="n">
         <v>18.9</v>
       </c>
       <c r="P19" t="n">
-        <v>25.5</v>
+        <v>25.7</v>
       </c>
       <c r="Q19" t="n">
-        <v>0.741</v>
+        <v>0.737</v>
       </c>
       <c r="R19" t="n">
-        <v>12.4</v>
+        <v>12.5</v>
       </c>
       <c r="S19" t="n">
         <v>28.5</v>
       </c>
       <c r="T19" t="n">
-        <v>40.9</v>
+        <v>41.1</v>
       </c>
       <c r="U19" t="n">
         <v>22.3</v>
       </c>
       <c r="V19" t="n">
-        <v>15.2</v>
+        <v>15.1</v>
       </c>
       <c r="W19" t="n">
         <v>9.1</v>
@@ -3824,16 +3891,16 @@
         <v>20.3</v>
       </c>
       <c r="AA19" t="n">
-        <v>22</v>
+        <v>22.1</v>
       </c>
       <c r="AB19" t="n">
-        <v>98.5</v>
+        <v>98.2</v>
       </c>
       <c r="AC19" t="n">
-        <v>-9.6</v>
+        <v>-10.1</v>
       </c>
       <c r="AD19" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="AE19" t="n">
         <v>29</v>
@@ -3845,7 +3912,7 @@
         <v>29</v>
       </c>
       <c r="AH19" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AI19" t="n">
         <v>16</v>
@@ -3863,16 +3930,16 @@
         <v>30</v>
       </c>
       <c r="AN19" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AO19" t="n">
         <v>5</v>
       </c>
       <c r="AP19" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AQ19" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AR19" t="n">
         <v>3</v>
@@ -3881,7 +3948,7 @@
         <v>29</v>
       </c>
       <c r="AT19" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AU19" t="n">
         <v>11</v>
@@ -3905,7 +3972,7 @@
         <v>4</v>
       </c>
       <c r="BB19" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BC19" t="n">
         <v>29</v>
@@ -3920,7 +3987,7 @@
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>1-13-2014-15</t>
+          <t>2015-01-13</t>
         </is>
       </c>
     </row>
@@ -3937,16 +4004,16 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E20" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F20" t="n">
         <v>19</v>
       </c>
       <c r="G20" t="n">
-        <v>0.472</v>
+        <v>0.486</v>
       </c>
       <c r="H20" t="n">
         <v>48.3</v>
@@ -3955,88 +4022,88 @@
         <v>38.6</v>
       </c>
       <c r="J20" t="n">
-        <v>84.09999999999999</v>
+        <v>84.5</v>
       </c>
       <c r="K20" t="n">
-        <v>0.459</v>
+        <v>0.457</v>
       </c>
       <c r="L20" t="n">
-        <v>6.7</v>
+        <v>6.6</v>
       </c>
       <c r="M20" t="n">
         <v>19.3</v>
       </c>
       <c r="N20" t="n">
-        <v>0.346</v>
+        <v>0.344</v>
       </c>
       <c r="O20" t="n">
-        <v>17.5</v>
+        <v>17.4</v>
       </c>
       <c r="P20" t="n">
-        <v>22.7</v>
+        <v>22.9</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.77</v>
+        <v>0.759</v>
       </c>
       <c r="R20" t="n">
-        <v>11.4</v>
+        <v>11.8</v>
       </c>
       <c r="S20" t="n">
-        <v>31.6</v>
+        <v>31.8</v>
       </c>
       <c r="T20" t="n">
-        <v>43</v>
+        <v>43.5</v>
       </c>
       <c r="U20" t="n">
-        <v>21.4</v>
+        <v>21.3</v>
       </c>
       <c r="V20" t="n">
-        <v>12.9</v>
+        <v>12.8</v>
       </c>
       <c r="W20" t="n">
         <v>7.4</v>
       </c>
       <c r="X20" t="n">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="Y20" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="Z20" t="n">
         <v>19.5</v>
       </c>
       <c r="AA20" t="n">
-        <v>18.8</v>
+        <v>19</v>
       </c>
       <c r="AB20" t="n">
         <v>101.3</v>
       </c>
       <c r="AC20" t="n">
-        <v>-0.2</v>
+        <v>0.3</v>
       </c>
       <c r="AD20" t="n">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="AE20" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AF20" t="n">
         <v>13</v>
       </c>
       <c r="AG20" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AH20" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AI20" t="n">
         <v>10</v>
       </c>
       <c r="AJ20" t="n">
+        <v>12</v>
+      </c>
+      <c r="AK20" t="n">
         <v>13</v>
-      </c>
-      <c r="AK20" t="n">
-        <v>12</v>
       </c>
       <c r="AL20" t="n">
         <v>25</v>
@@ -4045,25 +4112,25 @@
         <v>23</v>
       </c>
       <c r="AN20" t="n">
+        <v>21</v>
+      </c>
+      <c r="AO20" t="n">
+        <v>15</v>
+      </c>
+      <c r="AP20" t="n">
         <v>17</v>
       </c>
-      <c r="AO20" t="n">
-        <v>14</v>
-      </c>
-      <c r="AP20" t="n">
-        <v>18</v>
-      </c>
       <c r="AQ20" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="AR20" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AS20" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AT20" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="AU20" t="n">
         <v>14</v>
@@ -4072,22 +4139,22 @@
         <v>6</v>
       </c>
       <c r="AW20" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AX20" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="AY20" t="n">
         <v>27</v>
       </c>
       <c r="AZ20" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BA20" t="n">
         <v>26</v>
       </c>
       <c r="BB20" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="BC20" t="n">
         <v>15</v>
@@ -4102,7 +4169,7 @@
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>1-13-2014-15</t>
+          <t>2015-01-13</t>
         </is>
       </c>
     </row>
@@ -4200,7 +4267,7 @@
         <v>2</v>
       </c>
       <c r="AE21" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AF21" t="n">
         <v>30</v>
@@ -4209,7 +4276,7 @@
         <v>30</v>
       </c>
       <c r="AH21" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AI21" t="n">
         <v>26</v>
@@ -4221,13 +4288,13 @@
         <v>21</v>
       </c>
       <c r="AL21" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AM21" t="n">
         <v>20</v>
       </c>
       <c r="AN21" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AO21" t="n">
         <v>30</v>
@@ -4236,7 +4303,7 @@
         <v>30</v>
       </c>
       <c r="AQ21" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AR21" t="n">
         <v>19</v>
@@ -4284,7 +4351,7 @@
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>1-13-2014-15</t>
+          <t>2015-01-13</t>
         </is>
       </c>
     </row>
@@ -4379,7 +4446,7 @@
         <v>0.8</v>
       </c>
       <c r="AD22" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="AE22" t="n">
         <v>15</v>
@@ -4397,7 +4464,7 @@
         <v>17</v>
       </c>
       <c r="AJ22" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AK22" t="n">
         <v>22</v>
@@ -4412,7 +4479,7 @@
         <v>28</v>
       </c>
       <c r="AO22" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AP22" t="n">
         <v>12</v>
@@ -4430,7 +4497,7 @@
         <v>2</v>
       </c>
       <c r="AU22" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AV22" t="n">
         <v>24</v>
@@ -4439,16 +4506,16 @@
         <v>23</v>
       </c>
       <c r="AX22" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AY22" t="n">
         <v>14</v>
       </c>
       <c r="AZ22" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="BA22" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="BB22" t="n">
         <v>19</v>
@@ -4466,7 +4533,7 @@
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>1-13-2014-15</t>
+          <t>2015-01-13</t>
         </is>
       </c>
     </row>
@@ -4483,94 +4550,94 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E23" t="n">
         <v>14</v>
       </c>
       <c r="F23" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G23" t="n">
-        <v>0.35</v>
+        <v>0.341</v>
       </c>
       <c r="H23" t="n">
         <v>48.1</v>
       </c>
       <c r="I23" t="n">
-        <v>36.9</v>
+        <v>36.7</v>
       </c>
       <c r="J23" t="n">
         <v>81</v>
       </c>
       <c r="K23" t="n">
-        <v>0.455</v>
+        <v>0.453</v>
       </c>
       <c r="L23" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="M23" t="n">
-        <v>19.1</v>
+        <v>18.9</v>
       </c>
       <c r="N23" t="n">
         <v>0.369</v>
       </c>
       <c r="O23" t="n">
-        <v>13.7</v>
+        <v>13.8</v>
       </c>
       <c r="P23" t="n">
         <v>19</v>
       </c>
       <c r="Q23" t="n">
-        <v>0.723</v>
+        <v>0.724</v>
       </c>
       <c r="R23" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="S23" t="n">
-        <v>31.8</v>
+        <v>32</v>
       </c>
       <c r="T23" t="n">
-        <v>40.4</v>
+        <v>40.8</v>
       </c>
       <c r="U23" t="n">
-        <v>20.2</v>
+        <v>20.1</v>
       </c>
       <c r="V23" t="n">
         <v>14.6</v>
       </c>
       <c r="W23" t="n">
-        <v>7.3</v>
+        <v>7.2</v>
       </c>
       <c r="X23" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="Y23" t="n">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="Z23" t="n">
-        <v>21.2</v>
+        <v>21.3</v>
       </c>
       <c r="AA23" t="n">
         <v>18.4</v>
       </c>
       <c r="AB23" t="n">
-        <v>94.5</v>
+        <v>94.2</v>
       </c>
       <c r="AC23" t="n">
-        <v>-5.2</v>
+        <v>-5.4</v>
       </c>
       <c r="AD23" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE23" t="n">
         <v>23</v>
       </c>
       <c r="AF23" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="AG23" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AH23" t="n">
         <v>28</v>
@@ -4579,16 +4646,16 @@
         <v>18</v>
       </c>
       <c r="AJ23" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AK23" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AL23" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AM23" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AN23" t="n">
         <v>7</v>
@@ -4603,7 +4670,7 @@
         <v>27</v>
       </c>
       <c r="AR23" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="AS23" t="n">
         <v>17</v>
@@ -4612,19 +4679,19 @@
         <v>28</v>
       </c>
       <c r="AU23" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AV23" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AW23" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AX23" t="n">
         <v>30</v>
       </c>
       <c r="AY23" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="AZ23" t="n">
         <v>19</v>
@@ -4648,7 +4715,7 @@
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>1-13-2014-15</t>
+          <t>2015-01-13</t>
         </is>
       </c>
     </row>
@@ -4665,37 +4732,37 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E24" t="n">
         <v>7</v>
       </c>
       <c r="F24" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G24" t="n">
-        <v>0.189</v>
+        <v>0.194</v>
       </c>
       <c r="H24" t="n">
         <v>48.3</v>
       </c>
       <c r="I24" t="n">
-        <v>33.2</v>
+        <v>33.3</v>
       </c>
       <c r="J24" t="n">
-        <v>81</v>
+        <v>81.09999999999999</v>
       </c>
       <c r="K24" t="n">
         <v>0.411</v>
       </c>
       <c r="L24" t="n">
-        <v>7.2</v>
+        <v>7.1</v>
       </c>
       <c r="M24" t="n">
         <v>23.8</v>
       </c>
       <c r="N24" t="n">
-        <v>0.301</v>
+        <v>0.299</v>
       </c>
       <c r="O24" t="n">
         <v>16.8</v>
@@ -4704,16 +4771,16 @@
         <v>24.7</v>
       </c>
       <c r="Q24" t="n">
-        <v>0.68</v>
+        <v>0.681</v>
       </c>
       <c r="R24" t="n">
         <v>11.6</v>
       </c>
       <c r="S24" t="n">
-        <v>30.2</v>
+        <v>30.4</v>
       </c>
       <c r="T24" t="n">
-        <v>41.9</v>
+        <v>42.1</v>
       </c>
       <c r="U24" t="n">
         <v>19.9</v>
@@ -4722,7 +4789,7 @@
         <v>19</v>
       </c>
       <c r="W24" t="n">
-        <v>9.9</v>
+        <v>10</v>
       </c>
       <c r="X24" t="n">
         <v>5.7</v>
@@ -4734,16 +4801,16 @@
         <v>21.8</v>
       </c>
       <c r="AA24" t="n">
-        <v>20.8</v>
+        <v>20.9</v>
       </c>
       <c r="AB24" t="n">
-        <v>90.5</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="AC24" t="n">
-        <v>-12.6</v>
+        <v>-12.5</v>
       </c>
       <c r="AD24" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="AE24" t="n">
         <v>28</v>
@@ -4755,22 +4822,22 @@
         <v>28</v>
       </c>
       <c r="AH24" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AI24" t="n">
         <v>30</v>
       </c>
       <c r="AJ24" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AK24" t="n">
         <v>30</v>
       </c>
       <c r="AL24" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AM24" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AN24" t="n">
         <v>30</v>
@@ -4779,7 +4846,7 @@
         <v>20</v>
       </c>
       <c r="AP24" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AQ24" t="n">
         <v>30</v>
@@ -4788,13 +4855,13 @@
         <v>8</v>
       </c>
       <c r="AS24" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AT24" t="n">
         <v>21</v>
       </c>
       <c r="AU24" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AV24" t="n">
         <v>30</v>
@@ -4803,10 +4870,10 @@
         <v>1</v>
       </c>
       <c r="AX24" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AY24" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AZ24" t="n">
         <v>23</v>
@@ -4830,7 +4897,7 @@
       </c>
       <c r="BF24" t="inlineStr">
         <is>
-          <t>1-13-2014-15</t>
+          <t>2015-01-13</t>
         </is>
       </c>
     </row>
@@ -4847,70 +4914,70 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E25" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F25" t="n">
         <v>18</v>
       </c>
       <c r="G25" t="n">
-        <v>0.5610000000000001</v>
+        <v>0.55</v>
       </c>
       <c r="H25" t="n">
-        <v>48.7</v>
+        <v>48.8</v>
       </c>
       <c r="I25" t="n">
         <v>39.9</v>
       </c>
       <c r="J25" t="n">
-        <v>86</v>
+        <v>86.2</v>
       </c>
       <c r="K25" t="n">
-        <v>0.464</v>
+        <v>0.462</v>
       </c>
       <c r="L25" t="n">
-        <v>9.800000000000001</v>
+        <v>9.9</v>
       </c>
       <c r="M25" t="n">
-        <v>27.1</v>
+        <v>27.3</v>
       </c>
       <c r="N25" t="n">
         <v>0.361</v>
       </c>
       <c r="O25" t="n">
-        <v>17.5</v>
+        <v>17.4</v>
       </c>
       <c r="P25" t="n">
-        <v>22</v>
+        <v>21.8</v>
       </c>
       <c r="Q25" t="n">
-        <v>0.796</v>
+        <v>0.797</v>
       </c>
       <c r="R25" t="n">
         <v>10.6</v>
       </c>
       <c r="S25" t="n">
-        <v>31.7</v>
+        <v>31.9</v>
       </c>
       <c r="T25" t="n">
-        <v>42.3</v>
+        <v>42.5</v>
       </c>
       <c r="U25" t="n">
-        <v>20.8</v>
+        <v>20.7</v>
       </c>
       <c r="V25" t="n">
-        <v>15.2</v>
+        <v>15.4</v>
       </c>
       <c r="W25" t="n">
         <v>8.699999999999999</v>
       </c>
       <c r="X25" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="Y25" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="Z25" t="n">
         <v>22.7</v>
@@ -4922,13 +4989,13 @@
         <v>107</v>
       </c>
       <c r="AC25" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AD25" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE25" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AF25" t="n">
         <v>12</v>
@@ -4937,31 +5004,31 @@
         <v>12</v>
       </c>
       <c r="AH25" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AI25" t="n">
         <v>4</v>
       </c>
       <c r="AJ25" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AK25" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AL25" t="n">
         <v>5</v>
       </c>
       <c r="AM25" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AN25" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AO25" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AP25" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AQ25" t="n">
         <v>1</v>
@@ -4970,37 +5037,37 @@
         <v>18</v>
       </c>
       <c r="AS25" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AT25" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="AU25" t="n">
         <v>21</v>
       </c>
       <c r="AV25" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AW25" t="n">
         <v>7</v>
       </c>
       <c r="AX25" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AY25" t="n">
         <v>6</v>
       </c>
       <c r="AZ25" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="BA25" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BB25" t="n">
         <v>4</v>
       </c>
       <c r="BC25" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BD25" t="n">
         <v>10</v>
@@ -5012,7 +5079,7 @@
       </c>
       <c r="BF25" t="inlineStr">
         <is>
-          <t>1-13-2014-15</t>
+          <t>2015-01-13</t>
         </is>
       </c>
     </row>
@@ -5107,7 +5174,7 @@
         <v>7.4</v>
       </c>
       <c r="AD26" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AE26" t="n">
         <v>1</v>
@@ -5125,7 +5192,7 @@
         <v>6</v>
       </c>
       <c r="AJ26" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AK26" t="n">
         <v>17</v>
@@ -5134,7 +5201,7 @@
         <v>3</v>
       </c>
       <c r="AM26" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AN26" t="n">
         <v>5</v>
@@ -5164,7 +5231,7 @@
         <v>10</v>
       </c>
       <c r="AW26" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AX26" t="n">
         <v>8</v>
@@ -5194,7 +5261,7 @@
       </c>
       <c r="BF26" t="inlineStr">
         <is>
-          <t>1-13-2014-15</t>
+          <t>2015-01-13</t>
         </is>
       </c>
     </row>
@@ -5211,97 +5278,97 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E27" t="n">
         <v>16</v>
       </c>
       <c r="F27" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G27" t="n">
-        <v>0.421</v>
+        <v>0.432</v>
       </c>
       <c r="H27" t="n">
-        <v>48.8</v>
+        <v>48.7</v>
       </c>
       <c r="I27" t="n">
-        <v>36.8</v>
+        <v>36.7</v>
       </c>
       <c r="J27" t="n">
-        <v>80.2</v>
+        <v>80</v>
       </c>
       <c r="K27" t="n">
         <v>0.459</v>
       </c>
       <c r="L27" t="n">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="M27" t="n">
-        <v>15.6</v>
+        <v>15.5</v>
       </c>
       <c r="N27" t="n">
-        <v>0.336</v>
+        <v>0.344</v>
       </c>
       <c r="O27" t="n">
-        <v>23.5</v>
+        <v>23.4</v>
       </c>
       <c r="P27" t="n">
-        <v>30.3</v>
+        <v>30.2</v>
       </c>
       <c r="Q27" t="n">
-        <v>0.775</v>
+        <v>0.774</v>
       </c>
       <c r="R27" t="n">
-        <v>11.1</v>
+        <v>11</v>
       </c>
       <c r="S27" t="n">
-        <v>33.9</v>
+        <v>33.5</v>
       </c>
       <c r="T27" t="n">
-        <v>44.9</v>
+        <v>44.5</v>
       </c>
       <c r="U27" t="n">
         <v>19.8</v>
       </c>
       <c r="V27" t="n">
-        <v>16.3</v>
+        <v>16.2</v>
       </c>
       <c r="W27" t="n">
         <v>6.5</v>
       </c>
       <c r="X27" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="Y27" t="n">
         <v>6.2</v>
       </c>
       <c r="Z27" t="n">
-        <v>21.9</v>
+        <v>21.8</v>
       </c>
       <c r="AA27" t="n">
         <v>25.4</v>
       </c>
       <c r="AB27" t="n">
-        <v>102.3</v>
+        <v>102.2</v>
       </c>
       <c r="AC27" t="n">
         <v>-1.5</v>
       </c>
       <c r="AD27" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="AE27" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AF27" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AG27" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AH27" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="AI27" t="n">
         <v>19</v>
@@ -5310,16 +5377,16 @@
         <v>28</v>
       </c>
       <c r="AK27" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AL27" t="n">
         <v>29</v>
       </c>
       <c r="AM27" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AN27" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="AO27" t="n">
         <v>1</v>
@@ -5328,16 +5395,16 @@
         <v>1</v>
       </c>
       <c r="AQ27" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AR27" t="n">
         <v>14</v>
       </c>
       <c r="AS27" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AT27" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AU27" t="n">
         <v>29</v>
@@ -5361,10 +5428,10 @@
         <v>1</v>
       </c>
       <c r="BB27" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BC27" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="BD27" t="n">
         <v>10</v>
@@ -5376,7 +5443,7 @@
       </c>
       <c r="BF27" t="inlineStr">
         <is>
-          <t>1-13-2014-15</t>
+          <t>2015-01-13</t>
         </is>
       </c>
     </row>
@@ -5396,13 +5463,13 @@
         <v>38</v>
       </c>
       <c r="E28" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F28" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G28" t="n">
-        <v>0.579</v>
+        <v>0.605</v>
       </c>
       <c r="H28" t="n">
         <v>49.2</v>
@@ -5411,70 +5478,70 @@
         <v>38.5</v>
       </c>
       <c r="J28" t="n">
-        <v>83.2</v>
+        <v>82.5</v>
       </c>
       <c r="K28" t="n">
-        <v>0.463</v>
+        <v>0.467</v>
       </c>
       <c r="L28" t="n">
-        <v>8.1</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="M28" t="n">
-        <v>22</v>
+        <v>21.9</v>
       </c>
       <c r="N28" t="n">
-        <v>0.369</v>
+        <v>0.375</v>
       </c>
       <c r="O28" t="n">
-        <v>16.9</v>
+        <v>17</v>
       </c>
       <c r="P28" t="n">
-        <v>22.3</v>
+        <v>22.4</v>
       </c>
       <c r="Q28" t="n">
-        <v>0.756</v>
+        <v>0.758</v>
       </c>
       <c r="R28" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="S28" t="n">
-        <v>33.9</v>
+        <v>34</v>
       </c>
       <c r="T28" t="n">
-        <v>43.7</v>
+        <v>43.8</v>
       </c>
       <c r="U28" t="n">
         <v>24.3</v>
       </c>
       <c r="V28" t="n">
-        <v>14.5</v>
+        <v>14.8</v>
       </c>
       <c r="W28" t="n">
-        <v>7.4</v>
+        <v>7.5</v>
       </c>
       <c r="X28" t="n">
         <v>5.4</v>
       </c>
       <c r="Y28" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="Z28" t="n">
-        <v>19.5</v>
+        <v>19.6</v>
       </c>
       <c r="AA28" t="n">
-        <v>20.4</v>
+        <v>20.5</v>
       </c>
       <c r="AB28" t="n">
-        <v>102.1</v>
+        <v>102.3</v>
       </c>
       <c r="AC28" t="n">
-        <v>3.6</v>
+        <v>3.9</v>
       </c>
       <c r="AD28" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AE28" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AF28" t="n">
         <v>11</v>
@@ -5489,13 +5556,13 @@
         <v>11</v>
       </c>
       <c r="AJ28" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AK28" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="AL28" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AM28" t="n">
         <v>15</v>
@@ -5525,7 +5592,7 @@
         <v>6</v>
       </c>
       <c r="AV28" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="AW28" t="n">
         <v>16</v>
@@ -5537,16 +5604,16 @@
         <v>10</v>
       </c>
       <c r="AZ28" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BA28" t="n">
         <v>18</v>
       </c>
       <c r="BB28" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BC28" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BD28" t="n">
         <v>10</v>
@@ -5558,7 +5625,7 @@
       </c>
       <c r="BF28" t="inlineStr">
         <is>
-          <t>1-13-2014-15</t>
+          <t>2015-01-13</t>
         </is>
       </c>
     </row>
@@ -5653,25 +5720,25 @@
         <v>5.9</v>
       </c>
       <c r="AD29" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="AE29" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AF29" t="n">
+        <v>6</v>
+      </c>
+      <c r="AG29" t="n">
         <v>7</v>
       </c>
-      <c r="AG29" t="n">
-        <v>8</v>
-      </c>
       <c r="AH29" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AI29" t="n">
         <v>5</v>
       </c>
       <c r="AJ29" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AK29" t="n">
         <v>10</v>
@@ -5683,7 +5750,7 @@
         <v>7</v>
       </c>
       <c r="AN29" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AO29" t="n">
         <v>3</v>
@@ -5710,25 +5777,25 @@
         <v>3</v>
       </c>
       <c r="AW29" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AX29" t="n">
         <v>20</v>
       </c>
       <c r="AY29" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AZ29" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BA29" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="BB29" t="n">
         <v>3</v>
       </c>
       <c r="BC29" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="BD29" t="n">
         <v>10</v>
@@ -5740,7 +5807,7 @@
       </c>
       <c r="BF29" t="inlineStr">
         <is>
-          <t>1-13-2014-15</t>
+          <t>2015-01-13</t>
         </is>
       </c>
     </row>
@@ -5757,28 +5824,28 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E30" t="n">
         <v>13</v>
       </c>
       <c r="F30" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G30" t="n">
-        <v>0.333</v>
+        <v>0.342</v>
       </c>
       <c r="H30" t="n">
         <v>48</v>
       </c>
       <c r="I30" t="n">
-        <v>35.8</v>
+        <v>35.7</v>
       </c>
       <c r="J30" t="n">
-        <v>78.7</v>
+        <v>78.59999999999999</v>
       </c>
       <c r="K30" t="n">
-        <v>0.455</v>
+        <v>0.454</v>
       </c>
       <c r="L30" t="n">
         <v>6.8</v>
@@ -5796,7 +5863,7 @@
         <v>23.8</v>
       </c>
       <c r="Q30" t="n">
-        <v>0.75</v>
+        <v>0.748</v>
       </c>
       <c r="R30" t="n">
         <v>11.5</v>
@@ -5808,7 +5875,7 @@
         <v>42.4</v>
       </c>
       <c r="U30" t="n">
-        <v>20</v>
+        <v>20.2</v>
       </c>
       <c r="V30" t="n">
         <v>15.2</v>
@@ -5826,16 +5893,16 @@
         <v>18.8</v>
       </c>
       <c r="AA30" t="n">
-        <v>19.8</v>
+        <v>19.9</v>
       </c>
       <c r="AB30" t="n">
-        <v>96.2</v>
+        <v>96</v>
       </c>
       <c r="AC30" t="n">
-        <v>-3.3</v>
+        <v>-3.1</v>
       </c>
       <c r="AD30" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AE30" t="n">
         <v>25</v>
@@ -5844,7 +5911,7 @@
         <v>25</v>
       </c>
       <c r="AG30" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AH30" t="n">
         <v>29</v>
@@ -5856,7 +5923,7 @@
         <v>29</v>
       </c>
       <c r="AK30" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AL30" t="n">
         <v>23</v>
@@ -5868,25 +5935,25 @@
         <v>24</v>
       </c>
       <c r="AO30" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AP30" t="n">
         <v>13</v>
       </c>
       <c r="AQ30" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AR30" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AS30" t="n">
         <v>23</v>
       </c>
       <c r="AT30" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AU30" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AV30" t="n">
         <v>23</v>
@@ -5895,7 +5962,7 @@
         <v>25</v>
       </c>
       <c r="AX30" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AY30" t="n">
         <v>11</v>
@@ -5904,10 +5971,10 @@
         <v>5</v>
       </c>
       <c r="BA30" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BB30" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BC30" t="n">
         <v>24</v>
@@ -5922,7 +5989,7 @@
       </c>
       <c r="BF30" t="inlineStr">
         <is>
-          <t>1-13-2014-15</t>
+          <t>2015-01-13</t>
         </is>
       </c>
     </row>
@@ -5939,16 +6006,16 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E31" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F31" t="n">
         <v>12</v>
       </c>
       <c r="G31" t="n">
-        <v>0.6840000000000001</v>
+        <v>0.676</v>
       </c>
       <c r="H31" t="n">
         <v>48.4</v>
@@ -5957,7 +6024,7 @@
         <v>38.9</v>
       </c>
       <c r="J31" t="n">
-        <v>82.2</v>
+        <v>82.40000000000001</v>
       </c>
       <c r="K31" t="n">
         <v>0.473</v>
@@ -5966,70 +6033,70 @@
         <v>6.1</v>
       </c>
       <c r="M31" t="n">
-        <v>15.5</v>
+        <v>15.6</v>
       </c>
       <c r="N31" t="n">
-        <v>0.394</v>
+        <v>0.392</v>
       </c>
       <c r="O31" t="n">
-        <v>15.7</v>
+        <v>15.6</v>
       </c>
       <c r="P31" t="n">
-        <v>21.2</v>
+        <v>21.1</v>
       </c>
       <c r="Q31" t="n">
-        <v>0.741</v>
+        <v>0.737</v>
       </c>
       <c r="R31" t="n">
         <v>10.4</v>
       </c>
       <c r="S31" t="n">
-        <v>32.6</v>
+        <v>32.4</v>
       </c>
       <c r="T31" t="n">
-        <v>42.9</v>
+        <v>42.8</v>
       </c>
       <c r="U31" t="n">
-        <v>24.8</v>
+        <v>25</v>
       </c>
       <c r="V31" t="n">
         <v>14.6</v>
       </c>
       <c r="W31" t="n">
-        <v>7.8</v>
+        <v>7.9</v>
       </c>
       <c r="X31" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="Y31" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="Z31" t="n">
-        <v>21</v>
+        <v>21.2</v>
       </c>
       <c r="AA31" t="n">
-        <v>20.3</v>
+        <v>20.4</v>
       </c>
       <c r="AB31" t="n">
         <v>99.59999999999999</v>
       </c>
       <c r="AC31" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AD31" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="AE31" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AF31" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AG31" t="n">
         <v>7</v>
       </c>
       <c r="AH31" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AI31" t="n">
         <v>8</v>
@@ -6038,13 +6105,13 @@
         <v>19</v>
       </c>
       <c r="AK31" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AL31" t="n">
         <v>26</v>
       </c>
       <c r="AM31" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AN31" t="n">
         <v>1</v>
@@ -6059,7 +6126,7 @@
         <v>24</v>
       </c>
       <c r="AR31" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AS31" t="n">
         <v>14</v>
@@ -6071,7 +6138,7 @@
         <v>4</v>
       </c>
       <c r="AV31" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AW31" t="n">
         <v>12</v>
@@ -6080,19 +6147,19 @@
         <v>9</v>
       </c>
       <c r="AY31" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AZ31" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="BA31" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="BB31" t="n">
         <v>18</v>
       </c>
       <c r="BC31" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BD31" t="n">
         <v>10</v>
@@ -6104,7 +6171,7 @@
       </c>
       <c r="BF31" t="inlineStr">
         <is>
-          <t>1-13-2014-15</t>
+          <t>2015-01-13</t>
         </is>
       </c>
     </row>
